--- a/manuscript/tables/e-table-2-key-variables.xlsx
+++ b/manuscript/tables/e-table-2-key-variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/newer-glp1-dementia-repkit/manuscript/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/Gwen's Documents/Work/Boston University GRA/Projects/GLP1s for AD/03_analysis/repository/newer-glp1-dementia-repkit/manuscript/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9335E5CA-0AB7-9747-9DD2-443839A1301A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B461C601-1547-7A49-A12B-284933DAB8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
+    <workbookView xWindow="3640" yWindow="22260" windowWidth="30240" windowHeight="18980" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
   </bookViews>
   <sheets>
     <sheet name="Key Variables" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
   <si>
     <t>Variable</t>
   </si>
@@ -191,9 +191,6 @@
     <t>90935-90999, 99512, 49420, 49421, 90945, 90947, 36145, 36800, 36810, 36815, 36831, 36832, 36833, 36838, 90935, 90937, 90939, 90940, 93990, 99512, A4653, A4671, A4672, A4673, A4719, A4720, A4721, A4722, A4723, A4724, A4725, A4726, A4728, A4760, A4765, A4766, A4860, A4880, A4900, A4901, A4905, E1632, E1592, E1594, E1630, E1634, E1638, E1640</t>
   </si>
   <si>
-    <t>Heart failure</t>
-  </si>
-  <si>
     <t>Hepatic disease</t>
   </si>
   <si>
@@ -209,9 +206,6 @@
     <t>Use of pacemakers of defibrillators</t>
   </si>
   <si>
-    <t>I50</t>
-  </si>
-  <si>
     <t>K70-K77, B16-B19</t>
   </si>
   <si>
@@ -279,6 +273,42 @@
   </si>
   <si>
     <t>Negative control outcomes</t>
+  </si>
+  <si>
+    <t>Z74.0, Z74.1, Z74.2, Z74.3, Z74.8, Z74.9, Z99</t>
+  </si>
+  <si>
+    <t>Care-provider dependency and limited mobility</t>
+  </si>
+  <si>
+    <t>Fractures</t>
+  </si>
+  <si>
+    <t>M484, M495, M80, M843, M844, M907, M966, S02, S12, S22, S32, S42, S52, S62, S72, S82, S92, T02, T08, T10, T12, T142</t>
+  </si>
+  <si>
+    <t>Malnutrition</t>
+  </si>
+  <si>
+    <t>E40, E41, E42, E43, E44, E45, E46</t>
+  </si>
+  <si>
+    <t>Acute kidney injury</t>
+  </si>
+  <si>
+    <t>N17</t>
+  </si>
+  <si>
+    <t>Proteinuria</t>
+  </si>
+  <si>
+    <t>R80</t>
+  </si>
+  <si>
+    <t>Heart failure (hospitalization only)</t>
+  </si>
+  <si>
+    <t>I50, I0981, I110, I130, I132</t>
   </si>
 </sst>
 </file>
@@ -477,8 +507,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}" name="Table1" displayName="Table1" ref="A1:D40" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D40" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}" name="Table1" displayName="Table1" ref="A1:D45" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D45" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{B0B29E94-BFDD-3C42-8ED5-F78E5C6AF6E7}" name="Step" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{05D7060B-B93D-CA4E-B901-F6FFF18D12B3}" name="Variable" dataDxfId="2"/>
@@ -806,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91BBE2C8-ED3D-B242-85C9-E05BBE5783B0}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" style="1" customWidth="1"/>
@@ -909,7 +939,7 @@
     </row>
     <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -976,10 +1006,10 @@
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D17" s="2"/>
     </row>
@@ -1016,10 +1046,10 @@
     <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -1038,10 +1068,10 @@
     <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D23" s="2"/>
     </row>
@@ -1090,10 +1120,10 @@
     <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D28" s="2"/>
     </row>
@@ -1123,7 +1153,7 @@
         <v>50</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31" s="2"/>
     </row>
@@ -1133,7 +1163,7 @@
         <v>51</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="2"/>
     </row>
@@ -1143,41 +1173,41 @@
         <v>52</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="119" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="1:4" ht="119" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>62</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
@@ -1189,35 +1219,85 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/manuscript/tables/e-table-2-key-variables.xlsx
+++ b/manuscript/tables/e-table-2-key-variables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/Gwen's Documents/Work/Boston University GRA/Projects/GLP1s for AD/03_analysis/repository/newer-glp1-dementia-repkit/manuscript/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B461C601-1547-7A49-A12B-284933DAB8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90010B0-A8C0-B247-A262-93B6E8948999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="22260" windowWidth="30240" windowHeight="18980" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16180" windowHeight="21600" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
   </bookViews>
   <sheets>
     <sheet name="Key Variables" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="95">
   <si>
     <t>Variable</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Step</t>
   </si>
   <si>
-    <t>Eligibility</t>
-  </si>
-  <si>
     <t>Type 1 diabetes</t>
   </si>
   <si>
@@ -80,15 +77,6 @@
     <t>Gastroparesis</t>
   </si>
   <si>
-    <t>K85, K86.0, K86.1, B25.2</t>
-  </si>
-  <si>
-    <t>C73, E31.2, Z85.850</t>
-  </si>
-  <si>
-    <t>K31.84</t>
-  </si>
-  <si>
     <t>Appendicitis</t>
   </si>
   <si>
@@ -104,15 +92,6 @@
     <t>K35</t>
   </si>
   <si>
-    <t>S02.5</t>
-  </si>
-  <si>
-    <t>G51.0</t>
-  </si>
-  <si>
-    <t>C44.01, C44.11, C44.21, C44.31, C44.41, C44.51, C44.61, C44.71, C44.81, C44.91</t>
-  </si>
-  <si>
     <t>Comorbidities</t>
   </si>
   <si>
@@ -125,9 +104,6 @@
     <t>Cancers</t>
   </si>
   <si>
-    <t>C00-C96</t>
-  </si>
-  <si>
     <t>Cerebrovascular disease</t>
   </si>
   <si>
@@ -143,9 +119,6 @@
     <t>Coronary revascularization</t>
   </si>
   <si>
-    <t>Z95.1-Z95.5, I25810</t>
-  </si>
-  <si>
     <t>CPT Codes</t>
   </si>
   <si>
@@ -155,9 +128,6 @@
     <t>Diabetic amputation</t>
   </si>
   <si>
-    <t>Z89.4, Z89.5</t>
-  </si>
-  <si>
     <t>Diabetic retinopathy</t>
   </si>
   <si>
@@ -170,24 +140,9 @@
     <t>Dyslipidemia</t>
   </si>
   <si>
-    <t>E11.3</t>
-  </si>
-  <si>
-    <t>E11.4</t>
-  </si>
-  <si>
-    <t>E16.0, E16.1, E16.2</t>
-  </si>
-  <si>
-    <t>E78, E88.1, E75.21, E75.22, E77.0, E77.1</t>
-  </si>
-  <si>
     <t>End-stage chronic kidney disease or dialysis</t>
   </si>
   <si>
-    <t>N18.5, N18.6, Z99.2, Z49, T85.611, T85.621, T85.631, T85.691, I95.3</t>
-  </si>
-  <si>
     <t>90935-90999, 99512, 49420, 49421, 90945, 90947, 36145, 36800, 36810, 36815, 36831, 36832, 36833, 36838, 90935, 90937, 90939, 90940, 93990, 99512, A4653, A4671, A4672, A4673, A4719, A4720, A4721, A4722, A4723, A4724, A4725, A4726, A4728, A4760, A4765, A4766, A4860, A4880, A4900, A4901, A4905, E1632, E1592, E1594, E1630, E1634, E1638, E1640</t>
   </si>
   <si>
@@ -209,18 +164,9 @@
     <t>K70-K77, B16-B19</t>
   </si>
   <si>
-    <t>I10-I16, I1A, N26.2</t>
-  </si>
-  <si>
     <t>I20-I25</t>
   </si>
   <si>
-    <t>K76.0</t>
-  </si>
-  <si>
-    <t>Z95.0, Z95.810, Z95.811, Z95.812</t>
-  </si>
-  <si>
     <t>33206-33249, 02H63JZ, 02H73JZ, 02HK3JZ, 0JH604Z, 0JPT0PZ, 0JH60PZ, 02HK3KZ, 0JH608Z, 0JPT0PZ, 0JH60KZ, 33262, 33263, 33264</t>
   </si>
   <si>
@@ -248,9 +194,6 @@
     <t>Sleep apnea</t>
   </si>
   <si>
-    <t>G47.3</t>
-  </si>
-  <si>
     <t>Thyroid disorders</t>
   </si>
   <si>
@@ -275,9 +218,6 @@
     <t>Negative control outcomes</t>
   </si>
   <si>
-    <t>Z74.0, Z74.1, Z74.2, Z74.3, Z74.8, Z74.9, Z99</t>
-  </si>
-  <si>
     <t>Care-provider dependency and limited mobility</t>
   </si>
   <si>
@@ -309,6 +249,81 @@
   </si>
   <si>
     <t>I50, I0981, I110, I130, I132</t>
+  </si>
+  <si>
+    <t>Mild cognitive impairment</t>
+  </si>
+  <si>
+    <t>G3184</t>
+  </si>
+  <si>
+    <t>K85, K860, K861, B252</t>
+  </si>
+  <si>
+    <t>C73, E312, Z85850</t>
+  </si>
+  <si>
+    <t>K3184</t>
+  </si>
+  <si>
+    <t>S025</t>
+  </si>
+  <si>
+    <t>G510</t>
+  </si>
+  <si>
+    <t>C4401, C4411, C4421, C4431, C4441, C4451, C4461, C4471, C4481, C4491</t>
+  </si>
+  <si>
+    <t>Z951-Z955, I25810</t>
+  </si>
+  <si>
+    <t>Z894, Z895</t>
+  </si>
+  <si>
+    <t>E113</t>
+  </si>
+  <si>
+    <t>E114</t>
+  </si>
+  <si>
+    <t>E78, E881, E7521, E7522, E770, E771</t>
+  </si>
+  <si>
+    <t>N185, N186, Z992, Z49, T85611, T85621, T85631, T85691, I953</t>
+  </si>
+  <si>
+    <t>E160, E161, E162</t>
+  </si>
+  <si>
+    <t>I10-I16, I1A, N262</t>
+  </si>
+  <si>
+    <t>K760</t>
+  </si>
+  <si>
+    <t>G473</t>
+  </si>
+  <si>
+    <t>Z950, Z95810, Z95811, Z95812</t>
+  </si>
+  <si>
+    <t>Z740, Z741, Z742, Z743, Z748, Z749, Z99</t>
+  </si>
+  <si>
+    <t>Exclusion criteria</t>
+  </si>
+  <si>
+    <t>Neuroimaging order</t>
+  </si>
+  <si>
+    <t>B030ZZZ, B020ZZZ</t>
+  </si>
+  <si>
+    <t>70551, 70552, 70553, 70555, 70450, 70460, 70470, 0865T, 0866T</t>
+  </si>
+  <si>
+    <t>C0-C9</t>
   </si>
 </sst>
 </file>
@@ -507,8 +522,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}" name="Table1" displayName="Table1" ref="A1:D45" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D45" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}" name="Table1" displayName="Table1" ref="A1:D47" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D47" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{B0B29E94-BFDD-3C42-8ED5-F78E5C6AF6E7}" name="Step" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{05D7060B-B93D-CA4E-B901-F6FFF18D12B3}" name="Variable" dataDxfId="2"/>
@@ -836,10 +851,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91BBE2C8-ED3D-B242-85C9-E05BBE5783B0}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" style="1" customWidth="1"/>
@@ -857,12 +872,12 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -871,40 +886,40 @@
     <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2"/>
       <c r="F6" s="2"/>
@@ -912,392 +927,414 @@
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+    <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="A12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="136" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" ht="289" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>49</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="289" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" ht="119" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D37" s="2"/>
-    </row>
-    <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
